--- a/задание/ПА/Задание 1/Products_import.xlsx
+++ b/задание/ПА/Задание 1/Products_import.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Elena\Downloads\1\2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10231323\Desktop\--2\задание\ПА\Задание 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299842CD-A94D-490B-8B68-F32401082A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12" yWindow="252" windowWidth="22968" windowHeight="11976" xr2:uid="{F0856EE8-34A5-44B5-A4A9-79DBAC53E381}"/>
+    <workbookView xWindow="15" yWindow="255" windowWidth="22965" windowHeight="11970"/>
   </bookViews>
   <sheets>
     <sheet name="Products_import" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="155">
   <si>
     <t>Категория</t>
   </si>
@@ -507,7 +506,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -863,22 +862,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E225750-C10A-40DC-A5CC-9E38343D647F}">
-  <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H74"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.21875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="63.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="47.5546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="64.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="63.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="23.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="47.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="64.140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="8" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
+    <col min="9" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -904,7 +903,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -917,8 +916,8 @@
       <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>12</v>
+      <c r="E2" s="1">
+        <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>13</v>
@@ -930,7 +929,7 @@
         <v>2190</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -943,8 +942,8 @@
       <c r="D3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
+      <c r="E3" s="1">
+        <v>2</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>18</v>
@@ -956,7 +955,7 @@
         <v>2490</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -969,8 +968,8 @@
       <c r="D4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>22</v>
+      <c r="E4" s="1">
+        <v>3</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>23</v>
@@ -982,7 +981,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -995,8 +994,8 @@
       <c r="D5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>28</v>
+      <c r="E5" s="1">
+        <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>29</v>
@@ -1008,7 +1007,7 @@
         <v>3490</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -1021,8 +1020,8 @@
       <c r="D6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>33</v>
+      <c r="E6" s="1">
+        <v>5</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>34</v>
@@ -1034,7 +1033,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -1047,8 +1046,8 @@
       <c r="D7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>38</v>
+      <c r="E7" s="1">
+        <v>6</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>39</v>
@@ -1060,7 +1059,7 @@
         <v>4290</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -1073,8 +1072,8 @@
       <c r="D8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>44</v>
+      <c r="E8" s="1">
+        <v>7</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>45</v>
@@ -1086,7 +1085,7 @@
         <v>2790</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -1099,8 +1098,8 @@
       <c r="D9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>49</v>
+      <c r="E9" s="1">
+        <v>8</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>50</v>
@@ -1112,7 +1111,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -1125,8 +1124,8 @@
       <c r="D10" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>55</v>
+      <c r="E10" s="1">
+        <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>56</v>
@@ -1138,7 +1137,7 @@
         <v>2390</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>58</v>
       </c>
@@ -1151,8 +1150,8 @@
       <c r="D11" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>61</v>
+      <c r="E11" s="1">
+        <v>10</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>62</v>
@@ -1164,7 +1163,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>58</v>
       </c>
@@ -1177,8 +1176,8 @@
       <c r="D12" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>61</v>
+      <c r="E12" s="1">
+        <v>10</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>66</v>
@@ -1190,7 +1189,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>58</v>
       </c>
@@ -1203,8 +1202,8 @@
       <c r="D13" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>70</v>
+      <c r="E13" s="1">
+        <v>11</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>71</v>
@@ -1216,7 +1215,7 @@
         <v>17000</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>58</v>
       </c>
@@ -1229,8 +1228,8 @@
       <c r="D14" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>75</v>
+      <c r="E14" s="1">
+        <v>12</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>76</v>
@@ -1242,7 +1241,7 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>58</v>
       </c>
@@ -1255,8 +1254,8 @@
       <c r="D15" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>80</v>
+      <c r="E15" s="1">
+        <v>13</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>81</v>
@@ -1268,7 +1267,7 @@
         <v>5600</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>58</v>
       </c>
@@ -1281,8 +1280,8 @@
       <c r="D16" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>85</v>
+      <c r="E16" s="1">
+        <v>14</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>86</v>
@@ -1294,7 +1293,7 @@
         <v>7130</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>58</v>
       </c>
@@ -1307,8 +1306,8 @@
       <c r="D17" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>85</v>
+      <c r="E17" s="1">
+        <v>14</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>90</v>
@@ -1320,7 +1319,7 @@
         <v>12340</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>58</v>
       </c>
@@ -1333,8 +1332,8 @@
       <c r="D18" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>80</v>
+      <c r="E18" s="1">
+        <v>13</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>94</v>
@@ -1346,7 +1345,7 @@
         <v>7757</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>58</v>
       </c>
@@ -1359,8 +1358,8 @@
       <c r="D19" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>75</v>
+      <c r="E19" s="1">
+        <v>12</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>98</v>
@@ -1372,7 +1371,7 @@
         <v>7550</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>58</v>
       </c>
@@ -1385,8 +1384,8 @@
       <c r="D20" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>17</v>
+      <c r="E20" s="1">
+        <v>2</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>102</v>
@@ -1398,7 +1397,7 @@
         <v>9450</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>58</v>
       </c>
@@ -1411,8 +1410,8 @@
       <c r="D21" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>17</v>
+      <c r="E21" s="1">
+        <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>105</v>
@@ -1424,7 +1423,7 @@
         <v>8565</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>58</v>
       </c>
@@ -1437,8 +1436,8 @@
       <c r="D22" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>75</v>
+      <c r="E22" s="1">
+        <v>12</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>109</v>
@@ -1450,7 +1449,7 @@
         <v>8765</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>58</v>
       </c>
@@ -1463,8 +1462,8 @@
       <c r="D23" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>75</v>
+      <c r="E23" s="1">
+        <v>12</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>113</v>
@@ -1476,7 +1475,7 @@
         <v>7795</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>115</v>
       </c>
@@ -1489,8 +1488,8 @@
       <c r="D24" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>118</v>
+      <c r="E24" s="1">
+        <v>15</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>119</v>
@@ -1502,7 +1501,7 @@
         <v>6550</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>115</v>
       </c>
@@ -1515,8 +1514,8 @@
       <c r="D25" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>118</v>
+      <c r="E25" s="1">
+        <v>15</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>123</v>
@@ -1528,7 +1527,7 @@
         <v>7890</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>115</v>
       </c>
@@ -1541,8 +1540,8 @@
       <c r="D26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>17</v>
+      <c r="E26" s="1">
+        <v>2</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>126</v>
@@ -1554,7 +1553,7 @@
         <v>9567</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>115</v>
       </c>
@@ -1567,8 +1566,8 @@
       <c r="D27" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>61</v>
+      <c r="E27" s="1">
+        <v>10</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>130</v>
@@ -1580,7 +1579,7 @@
         <v>24569</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>115</v>
       </c>
@@ -1593,8 +1592,8 @@
       <c r="D28" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>134</v>
+      <c r="E28" s="1">
+        <v>16</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>135</v>
@@ -1606,7 +1605,7 @@
         <v>10155</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>115</v>
       </c>
@@ -1619,8 +1618,8 @@
       <c r="D29" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>134</v>
+      <c r="E29" s="1">
+        <v>16</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>139</v>
@@ -1632,7 +1631,7 @@
         <v>25625</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>115</v>
       </c>
@@ -1645,8 +1644,8 @@
       <c r="D30" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>61</v>
+      <c r="E30" s="1">
+        <v>10</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>144</v>
@@ -1658,7 +1657,7 @@
         <v>21500</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>115</v>
       </c>
@@ -1671,8 +1670,8 @@
       <c r="D31" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>80</v>
+      <c r="E31" s="1">
+        <v>13</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>148</v>
@@ -1684,7 +1683,7 @@
         <v>14567</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>115</v>
       </c>
@@ -1697,8 +1696,8 @@
       <c r="D32" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>61</v>
+      <c r="E32" s="1">
+        <v>10</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>152</v>
@@ -1709,6 +1708,202 @@
       <c r="H32" s="2">
         <v>15670</v>
       </c>
+    </row>
+    <row r="43" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C43" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C46" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C47" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D47" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C48" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D48" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C49" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D49" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C50" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D50" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C51" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D51" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C52" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D52" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C53" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D53" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C54" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D54" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C55" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D55" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C56" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D56" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C57" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D57" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C58" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D58" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C59" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D59" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C60"/>
+      <c r="D60"/>
+    </row>
+    <row r="61" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C61"/>
+      <c r="D61"/>
+    </row>
+    <row r="62" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C62"/>
+      <c r="D62"/>
+    </row>
+    <row r="63" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C63"/>
+      <c r="D63"/>
+    </row>
+    <row r="64" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C64"/>
+      <c r="D64"/>
+    </row>
+    <row r="65" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C65"/>
+      <c r="D65"/>
+    </row>
+    <row r="66" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C66"/>
+      <c r="D66"/>
+    </row>
+    <row r="67" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C67"/>
+      <c r="D67"/>
+    </row>
+    <row r="68" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C68"/>
+      <c r="D68"/>
+    </row>
+    <row r="69" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C69"/>
+      <c r="D69"/>
+    </row>
+    <row r="70" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C70"/>
+      <c r="D70"/>
+    </row>
+    <row r="71" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C71"/>
+      <c r="D71"/>
+    </row>
+    <row r="72" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C72"/>
+      <c r="D72"/>
+    </row>
+    <row r="73" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C73"/>
+      <c r="D73"/>
+    </row>
+    <row r="74" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C74"/>
+      <c r="D74"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
